--- a/output/_temp/etapa_2_actualizacion_mensual/_interno/diagnostico_no_cruzados_rapido.xlsx
+++ b/output/_temp/etapa_2_actualizacion_mensual/_interno/diagnostico_no_cruzados_rapido.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,6 +461,84 @@
         <is>
           <t>COLUMNA_DIA_EXISTE</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MP-01A</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ASUB</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>SIN_COINCIDENCIA</t>
+        </is>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>NF</t>
+        </is>
+      </c>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MP-03C</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ASUB</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>SIN_COINCIDENCIA</t>
+        </is>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>NF</t>
+        </is>
+      </c>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/_temp/etapa_2_actualizacion_mensual/_interno/diagnostico_no_cruzados_rapido.xlsx
+++ b/output/_temp/etapa_2_actualizacion_mensual/_interno/diagnostico_no_cruzados_rapido.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MP-01A</t>
+          <t>MP-04A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -499,45 +499,6 @@
         <v>0</v>
       </c>
       <c r="I2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>MP-03C</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ASUB</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>SIN_COINCIDENCIA</t>
-        </is>
-      </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>NF</t>
-        </is>
-      </c>
-      <c r="H3" t="b">
-        <v>0</v>
-      </c>
-      <c r="I3" t="b">
         <v>1</v>
       </c>
     </row>

--- a/output/_temp/etapa_2_actualizacion_mensual/_interno/diagnostico_no_cruzados_rapido.xlsx
+++ b/output/_temp/etapa_2_actualizacion_mensual/_interno/diagnostico_no_cruzados_rapido.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,45 +461,6 @@
         <is>
           <t>COLUMNA_DIA_EXISTE</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>MP-04A</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>ASUB</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>13</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>SIN_COINCIDENCIA</t>
-        </is>
-      </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>NF</t>
-        </is>
-      </c>
-      <c r="H2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I2" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
